--- a/self_paced_reading/experiment/StimuliSPR.xlsx
+++ b/self_paced_reading/experiment/StimuliSPR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/fng1895_ads_northwestern_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rubydowling/Documents/GitHub/AdjunctControl26/self_paced_reading/experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{FCDDB2B5-3FDA-4B41-B822-B54319D119FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94F8B412-F359-CA44-B818-5105887817B8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A813EE-F693-D54C-9337-E27F406F3C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2120" yWindow="760" windowWidth="27240" windowHeight="16180" xr2:uid="{49F68F50-C0A0-2A43-B5F6-E3A97D82E26C}"/>
   </bookViews>
@@ -410,9 +410,6 @@
     <t>salesman</t>
   </si>
   <si>
-    <t>tower</t>
-  </si>
-  <si>
     <t>Comprising six difficult classes, the teacher will manage her busy schedule</t>
   </si>
   <si>
@@ -426,6 +423,9 @@
   </si>
   <si>
     <t>schedule</t>
+  </si>
+  <si>
+    <t>skyscraper</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1448,7 @@
         <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -1471,7 +1471,7 @@
         <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -1675,10 +1675,10 @@
         <v>7</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -1698,10 +1698,10 @@
         <v>7</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -1721,10 +1721,10 @@
         <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F40" t="s">
         <v>20</v>
@@ -1744,10 +1744,10 @@
         <v>7</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F41" t="s">
         <v>20</v>

--- a/self_paced_reading/experiment/StimuliSPR.xlsx
+++ b/self_paced_reading/experiment/StimuliSPR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rubydowling/Documents/GitHub/AdjunctControl26/self_paced_reading/experiment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aldos\OneDrive\Desktop\Projects\AdjunctControl26\self_paced_reading\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A813EE-F693-D54C-9337-E27F406F3C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233C2000-388E-4592-A1D1-7A3F9CC43425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2120" yWindow="760" windowWidth="27240" windowHeight="16180" xr2:uid="{49F68F50-C0A0-2A43-B5F6-E3A97D82E26C}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{49F68F50-C0A0-2A43-B5F6-E3A97D82E26C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="170">
   <si>
     <t>item</t>
   </si>
@@ -194,51 +194,12 @@
     <t>chef</t>
   </si>
   <si>
-    <t>The gopher chases the fearful rabbit</t>
-  </si>
-  <si>
-    <t>The musician plays the lovely violin</t>
-  </si>
-  <si>
-    <t>The woman washes the dirty dishes</t>
-  </si>
-  <si>
-    <t>The monkey eats the ripe banana</t>
-  </si>
-  <si>
-    <t>The wrecking ball demolishes the decrepit building</t>
-  </si>
-  <si>
-    <t>The horse chews the sweet apple</t>
-  </si>
-  <si>
-    <t>The librarian shelves the heavy book</t>
-  </si>
-  <si>
-    <t>The child plays the loud drums</t>
-  </si>
-  <si>
-    <t>The knight protects the guarded fortress</t>
-  </si>
-  <si>
-    <t>The editor mentors the stressed writer</t>
-  </si>
-  <si>
-    <t>The hammer smashes the fragile glass</t>
-  </si>
-  <si>
-    <t>The basket holds the expensive cheeses</t>
-  </si>
-  <si>
     <t>filler</t>
   </si>
   <si>
     <t>gopher</t>
   </si>
   <si>
-    <t>musician</t>
-  </si>
-  <si>
     <t>woman</t>
   </si>
   <si>
@@ -426,6 +387,165 @@
   </si>
   <si>
     <t>skyscraper</t>
+  </si>
+  <si>
+    <t>question_attribute</t>
+  </si>
+  <si>
+    <t>Was the brother mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Will the baker present the Baked Alaska?</t>
+  </si>
+  <si>
+    <t>correct_answer</t>
+  </si>
+  <si>
+    <t>Was the car mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Was the customer mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Will the salesman market the skyscraper?</t>
+  </si>
+  <si>
+    <t>Was tennis mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Were the girls mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Was the queen mentioned in the sentence?</t>
+  </si>
+  <si>
+    <t>Will the chef abandon his station?</t>
+  </si>
+  <si>
+    <t>Was a woman mentioned?</t>
+  </si>
+  <si>
+    <t>Was a whale mentioned?</t>
+  </si>
+  <si>
+    <t>Was a backpack mentioned?</t>
+  </si>
+  <si>
+    <t>Was a student mentioned?</t>
+  </si>
+  <si>
+    <t>Was a table mentioned?</t>
+  </si>
+  <si>
+    <t>Was a safe mentioned?</t>
+  </si>
+  <si>
+    <t>Was a coach mentioned?</t>
+  </si>
+  <si>
+    <t>Was a captain mentioned?</t>
+  </si>
+  <si>
+    <t>Was an assistant mentioned?</t>
+  </si>
+  <si>
+    <t>Was a  ball mentioned?</t>
+  </si>
+  <si>
+    <t>Was a engineer mentioned?</t>
+  </si>
+  <si>
+    <t>Was a cat mentioned?</t>
+  </si>
+  <si>
+    <t>Was a gala mentioned?</t>
+  </si>
+  <si>
+    <t>Was a basketball mentioned?</t>
+  </si>
+  <si>
+    <t>Will the author publish a new book?</t>
+  </si>
+  <si>
+    <t>Will the student study the tome poorly?</t>
+  </si>
+  <si>
+    <t>Are the teacher's classes easy?</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>The gopher chased the fearful rabbit</t>
+  </si>
+  <si>
+    <t>The woman washed the dirty dishes</t>
+  </si>
+  <si>
+    <t>The monkey ate the ripe banana</t>
+  </si>
+  <si>
+    <t>The wrecking ball demolished the decrepit building</t>
+  </si>
+  <si>
+    <t>The horse chewed the sweet apple</t>
+  </si>
+  <si>
+    <t>The librarian shelved the heavy book</t>
+  </si>
+  <si>
+    <t>The child played the loud drums</t>
+  </si>
+  <si>
+    <t>The knight protected the guarded fortress</t>
+  </si>
+  <si>
+    <t>The editor mentored the stressed writer</t>
+  </si>
+  <si>
+    <t>The hammer smashed the fragile glass</t>
+  </si>
+  <si>
+    <t>The basket held the expensive cheeses</t>
+  </si>
+  <si>
+    <t>Did the gopher chase the rabbit?</t>
+  </si>
+  <si>
+    <t>Did the woman wash the dishes?</t>
+  </si>
+  <si>
+    <t>Was the lovely violin played by the student?</t>
+  </si>
+  <si>
+    <t>The professor played the lovely violin</t>
+  </si>
+  <si>
+    <t>Was the building demolished?</t>
+  </si>
+  <si>
+    <t>Was the book heavy?</t>
+  </si>
+  <si>
+    <t>Was the fortress protected?</t>
+  </si>
+  <si>
+    <t>Was the writer relaxed?</t>
+  </si>
+  <si>
+    <t>Was the fragile glass smashed?</t>
+  </si>
+  <si>
+    <t>professor</t>
+  </si>
+  <si>
+    <t>Were the drums quiet?</t>
+  </si>
+  <si>
+    <t>Was the ripe banana eaten by a gopher?</t>
   </si>
 </sst>
 </file>
@@ -804,16 +924,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1162B0D9-BC05-C945-B9C7-11028D0466E0}">
-  <dimension ref="A1:G73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I73"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="4" max="4" width="95.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.1640625" customWidth="1"/>
+    <col min="4" max="4" width="95.6484375" customWidth="1"/>
+    <col min="5" max="5" width="17.1484375" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="48.34765625" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -835,8 +957,14 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -858,8 +986,14 @@
       <c r="G2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -881,8 +1015,14 @@
       <c r="G3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A4">
         <v>1</v>
       </c>
@@ -896,7 +1036,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
@@ -904,8 +1044,14 @@
       <c r="G4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>1</v>
       </c>
@@ -919,7 +1065,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -927,8 +1073,14 @@
       <c r="G5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>142</v>
+      </c>
+      <c r="I5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>2</v>
       </c>
@@ -950,8 +1102,14 @@
       <c r="G6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>2</v>
       </c>
@@ -973,8 +1131,14 @@
       <c r="G7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I7" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>2</v>
       </c>
@@ -988,7 +1152,7 @@
         <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="F8" t="s">
         <v>20</v>
@@ -996,8 +1160,14 @@
       <c r="G8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1011,7 +1181,7 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
@@ -1019,8 +1189,14 @@
       <c r="G9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1042,8 +1218,14 @@
       <c r="G10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A11">
         <v>3</v>
       </c>
@@ -1065,8 +1247,14 @@
       <c r="G11" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1080,7 +1268,7 @@
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F12" t="s">
         <v>20</v>
@@ -1088,8 +1276,14 @@
       <c r="G12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>3</v>
       </c>
@@ -1103,7 +1297,7 @@
         <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F13" t="s">
         <v>20</v>
@@ -1111,8 +1305,14 @@
       <c r="G13" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>119</v>
+      </c>
+      <c r="I13" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A14">
         <v>4</v>
       </c>
@@ -1123,10 +1323,10 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="F14" t="s">
         <v>10</v>
@@ -1134,8 +1334,14 @@
       <c r="G14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>4</v>
       </c>
@@ -1146,10 +1352,10 @@
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="F15" t="s">
         <v>10</v>
@@ -1157,8 +1363,14 @@
       <c r="G15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>143</v>
+      </c>
+      <c r="I15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>4</v>
       </c>
@@ -1169,10 +1381,10 @@
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="F16" t="s">
         <v>20</v>
@@ -1180,8 +1392,14 @@
       <c r="G16" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A17">
         <v>4</v>
       </c>
@@ -1192,10 +1410,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
@@ -1203,8 +1421,14 @@
       <c r="G17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A18">
         <v>5</v>
       </c>
@@ -1226,8 +1450,14 @@
       <c r="G18" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A19">
         <v>5</v>
       </c>
@@ -1249,8 +1479,14 @@
       <c r="G19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A20">
         <v>5</v>
       </c>
@@ -1264,7 +1500,7 @@
         <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
         <v>20</v>
@@ -1272,8 +1508,14 @@
       <c r="G20" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A21">
         <v>5</v>
       </c>
@@ -1287,7 +1529,7 @@
         <v>30</v>
       </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s">
         <v>20</v>
@@ -1295,8 +1537,14 @@
       <c r="G21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>121</v>
+      </c>
+      <c r="I21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A22">
         <v>6</v>
       </c>
@@ -1307,10 +1555,10 @@
         <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F22" t="s">
         <v>10</v>
@@ -1318,8 +1566,14 @@
       <c r="G22" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A23">
         <v>6</v>
       </c>
@@ -1330,10 +1584,10 @@
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
         <v>10</v>
@@ -1341,8 +1595,14 @@
       <c r="G23" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>122</v>
+      </c>
+      <c r="I23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A24">
         <v>6</v>
       </c>
@@ -1353,10 +1613,10 @@
         <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
         <v>20</v>
@@ -1364,8 +1624,14 @@
       <c r="G24" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>122</v>
+      </c>
+      <c r="I24" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A25">
         <v>6</v>
       </c>
@@ -1376,10 +1642,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="F25" t="s">
         <v>20</v>
@@ -1387,8 +1653,14 @@
       <c r="G25" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>122</v>
+      </c>
+      <c r="I25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A26">
         <v>7</v>
       </c>
@@ -1399,10 +1671,10 @@
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F26" t="s">
         <v>10</v>
@@ -1410,8 +1682,14 @@
       <c r="G26" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>123</v>
+      </c>
+      <c r="I26" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A27">
         <v>7</v>
       </c>
@@ -1422,10 +1700,10 @@
         <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s">
         <v>10</v>
@@ -1433,8 +1711,14 @@
       <c r="G27" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>123</v>
+      </c>
+      <c r="I27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A28">
         <v>7</v>
       </c>
@@ -1445,10 +1729,10 @@
         <v>7</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F28" t="s">
         <v>20</v>
@@ -1456,8 +1740,14 @@
       <c r="G28" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>123</v>
+      </c>
+      <c r="I28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A29">
         <v>7</v>
       </c>
@@ -1468,10 +1758,10 @@
         <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E29" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F29" t="s">
         <v>20</v>
@@ -1479,8 +1769,14 @@
       <c r="G29" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>123</v>
+      </c>
+      <c r="I29" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A30">
         <v>8</v>
       </c>
@@ -1502,8 +1798,14 @@
       <c r="G30" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I30" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A31">
         <v>8</v>
       </c>
@@ -1525,8 +1827,14 @@
       <c r="G31" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>124</v>
+      </c>
+      <c r="I31" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A32">
         <v>8</v>
       </c>
@@ -1540,7 +1848,7 @@
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="F32" t="s">
         <v>20</v>
@@ -1548,8 +1856,14 @@
       <c r="G32" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>124</v>
+      </c>
+      <c r="I32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A33">
         <v>8</v>
       </c>
@@ -1563,7 +1877,7 @@
         <v>35</v>
       </c>
       <c r="E33" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="F33" t="s">
         <v>20</v>
@@ -1571,8 +1885,14 @@
       <c r="G33" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>124</v>
+      </c>
+      <c r="I33" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A34">
         <v>9</v>
       </c>
@@ -1594,8 +1914,14 @@
       <c r="G34" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>125</v>
+      </c>
+      <c r="I34" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A35">
         <v>9</v>
       </c>
@@ -1617,8 +1943,14 @@
       <c r="G35" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>125</v>
+      </c>
+      <c r="I35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A36">
         <v>9</v>
       </c>
@@ -1632,7 +1964,7 @@
         <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F36" t="s">
         <v>20</v>
@@ -1640,8 +1972,14 @@
       <c r="G36" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>125</v>
+      </c>
+      <c r="I36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A37">
         <v>9</v>
       </c>
@@ -1655,7 +1993,7 @@
         <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F37" t="s">
         <v>20</v>
@@ -1663,8 +2001,14 @@
       <c r="G37" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I37" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A38">
         <v>10</v>
       </c>
@@ -1675,10 +2019,10 @@
         <v>7</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E38" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F38" t="s">
         <v>10</v>
@@ -1686,8 +2030,14 @@
       <c r="G38" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>144</v>
+      </c>
+      <c r="I38" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A39">
         <v>10</v>
       </c>
@@ -1698,10 +2048,10 @@
         <v>7</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="E39" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F39" t="s">
         <v>10</v>
@@ -1709,8 +2059,14 @@
       <c r="G39" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>144</v>
+      </c>
+      <c r="I39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A40">
         <v>10</v>
       </c>
@@ -1721,10 +2077,10 @@
         <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E40" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="F40" t="s">
         <v>20</v>
@@ -1732,8 +2088,14 @@
       <c r="G40" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
+        <v>144</v>
+      </c>
+      <c r="I40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A41">
         <v>10</v>
       </c>
@@ -1744,10 +2106,10 @@
         <v>7</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="E41" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="F41" t="s">
         <v>20</v>
@@ -1755,8 +2117,14 @@
       <c r="G41" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>144</v>
+      </c>
+      <c r="I41" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A42">
         <v>11</v>
       </c>
@@ -1778,8 +2146,14 @@
       <c r="G42" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>126</v>
+      </c>
+      <c r="I42" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A43">
         <v>11</v>
       </c>
@@ -1801,8 +2175,14 @@
       <c r="G43" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>126</v>
+      </c>
+      <c r="I43" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A44">
         <v>11</v>
       </c>
@@ -1824,8 +2204,14 @@
       <c r="G44" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>126</v>
+      </c>
+      <c r="I44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A45">
         <v>11</v>
       </c>
@@ -1847,8 +2233,14 @@
       <c r="G45" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>126</v>
+      </c>
+      <c r="I45" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A46">
         <v>12</v>
       </c>
@@ -1870,8 +2262,14 @@
       <c r="G46" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
+        <v>127</v>
+      </c>
+      <c r="I46" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A47">
         <v>12</v>
       </c>
@@ -1893,8 +2291,14 @@
       <c r="G47" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
+        <v>127</v>
+      </c>
+      <c r="I47" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A48">
         <v>12</v>
       </c>
@@ -1916,8 +2320,14 @@
       <c r="G48" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48" t="s">
+        <v>127</v>
+      </c>
+      <c r="I48" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A49">
         <v>12</v>
       </c>
@@ -1939,8 +2349,14 @@
       <c r="G49" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49" t="s">
+        <v>127</v>
+      </c>
+      <c r="I49" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A50">
         <v>1001</v>
       </c>
@@ -1948,16 +2364,22 @@
         <v>1001</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="H50" t="s">
+        <v>158</v>
+      </c>
+      <c r="I50" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A51">
         <v>1002</v>
       </c>
@@ -1965,16 +2387,22 @@
         <v>1002</v>
       </c>
       <c r="C51" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>53</v>
+        <v>161</v>
       </c>
       <c r="E51" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+      <c r="H51" t="s">
+        <v>160</v>
+      </c>
+      <c r="I51" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A52">
         <v>1003</v>
       </c>
@@ -1982,16 +2410,22 @@
         <v>1003</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E52" t="s">
         <v>54</v>
       </c>
-      <c r="E52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52" t="s">
+        <v>159</v>
+      </c>
+      <c r="I52" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A53">
         <v>1004</v>
       </c>
@@ -1999,16 +2433,22 @@
         <v>1004</v>
       </c>
       <c r="C53" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" t="s">
         <v>55</v>
       </c>
-      <c r="E53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53" t="s">
+        <v>169</v>
+      </c>
+      <c r="I53" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A54">
         <v>1005</v>
       </c>
@@ -2016,16 +2456,22 @@
         <v>1005</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E54" t="s">
         <v>56</v>
       </c>
-      <c r="E54" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54" t="s">
+        <v>162</v>
+      </c>
+      <c r="I54" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A55">
         <v>1006</v>
       </c>
@@ -2033,16 +2479,22 @@
         <v>1006</v>
       </c>
       <c r="C55" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D55" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E55" t="s">
         <v>57</v>
       </c>
-      <c r="E55" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
+        <v>129</v>
+      </c>
+      <c r="I55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A56">
         <v>1007</v>
       </c>
@@ -2050,16 +2502,22 @@
         <v>1007</v>
       </c>
       <c r="C56" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E56" t="s">
         <v>58</v>
       </c>
-      <c r="E56" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56" t="s">
+        <v>163</v>
+      </c>
+      <c r="I56" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A57">
         <v>1008</v>
       </c>
@@ -2067,16 +2525,22 @@
         <v>1008</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D57" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" t="s">
         <v>59</v>
       </c>
-      <c r="E57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57" t="s">
+        <v>168</v>
+      </c>
+      <c r="I57" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A58">
         <v>1009</v>
       </c>
@@ -2084,16 +2548,22 @@
         <v>1009</v>
       </c>
       <c r="C58" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D58" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E58" t="s">
         <v>60</v>
       </c>
-      <c r="E58" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58" t="s">
+        <v>164</v>
+      </c>
+      <c r="I58" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A59">
         <v>1010</v>
       </c>
@@ -2101,16 +2571,22 @@
         <v>1010</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E59" t="s">
         <v>61</v>
       </c>
-      <c r="E59" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59" t="s">
+        <v>165</v>
+      </c>
+      <c r="I59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A60">
         <v>1011</v>
       </c>
@@ -2118,16 +2594,22 @@
         <v>1011</v>
       </c>
       <c r="C60" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E60" t="s">
         <v>62</v>
       </c>
-      <c r="E60" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60" t="s">
+        <v>166</v>
+      </c>
+      <c r="I60" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A61">
         <v>1012</v>
       </c>
@@ -2135,16 +2617,22 @@
         <v>1012</v>
       </c>
       <c r="C61" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D61" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E61" t="s">
         <v>63</v>
       </c>
-      <c r="E61" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61" t="s">
+        <v>130</v>
+      </c>
+      <c r="I61" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A62">
         <v>1013</v>
       </c>
@@ -2152,16 +2640,22 @@
         <v>1013</v>
       </c>
       <c r="C62" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="E62" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="H62" t="s">
+        <v>131</v>
+      </c>
+      <c r="I62" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A63">
         <v>1014</v>
       </c>
@@ -2169,16 +2663,22 @@
         <v>1014</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E63" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s">
+        <v>132</v>
+      </c>
+      <c r="I63" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A64">
         <v>1015</v>
       </c>
@@ -2186,16 +2686,22 @@
         <v>1015</v>
       </c>
       <c r="C64" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E64" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="H64" t="s">
+        <v>133</v>
+      </c>
+      <c r="I64" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A65">
         <v>1016</v>
       </c>
@@ -2203,16 +2709,22 @@
         <v>1016</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E65" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+      <c r="H65" t="s">
+        <v>134</v>
+      </c>
+      <c r="I65" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A66">
         <v>1017</v>
       </c>
@@ -2220,16 +2732,22 @@
         <v>1017</v>
       </c>
       <c r="C66" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E66" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+      <c r="H66" t="s">
+        <v>135</v>
+      </c>
+      <c r="I66" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A67">
         <v>1018</v>
       </c>
@@ -2237,16 +2755,22 @@
         <v>1018</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E67" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s">
+        <v>128</v>
+      </c>
+      <c r="I67" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A68">
         <v>1019</v>
       </c>
@@ -2254,16 +2778,22 @@
         <v>1019</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E68" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+      <c r="H68" t="s">
+        <v>136</v>
+      </c>
+      <c r="I68" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A69">
         <v>1020</v>
       </c>
@@ -2271,16 +2801,22 @@
         <v>1020</v>
       </c>
       <c r="C69" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E69" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+      <c r="H69" t="s">
+        <v>137</v>
+      </c>
+      <c r="I69" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A70">
         <v>1021</v>
       </c>
@@ -2288,16 +2824,22 @@
         <v>1021</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E70" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="H70" t="s">
+        <v>138</v>
+      </c>
+      <c r="I70" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A71">
         <v>1022</v>
       </c>
@@ -2305,16 +2847,22 @@
         <v>1022</v>
       </c>
       <c r="C71" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E71" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="H71" t="s">
+        <v>139</v>
+      </c>
+      <c r="I71" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A72">
         <v>1023</v>
       </c>
@@ -2322,16 +2870,22 @@
         <v>1023</v>
       </c>
       <c r="C72" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E72" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+      <c r="H72" t="s">
+        <v>140</v>
+      </c>
+      <c r="I72" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.6">
       <c r="A73">
         <v>1024</v>
       </c>
@@ -2339,13 +2893,19 @@
         <v>1024</v>
       </c>
       <c r="C73" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E73" t="s">
-        <v>100</v>
+        <v>87</v>
+      </c>
+      <c r="H73" t="s">
+        <v>141</v>
+      </c>
+      <c r="I73" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
